--- a/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T14:13:57+00:00</t>
+    <t>2025-05-20T08:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T08:55:00+00:00</t>
+    <t>2025-05-21T07:47:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:22+00:00</t>
+    <t>2025-05-21T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:53+00:00</t>
+    <t>2025-05-21T07:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:49:53+00:00</t>
+    <t>2025-05-21T07:50:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:50:26+00:00</t>
+    <t>2025-05-21T07:51:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:51:14+00:00</t>
+    <t>2025-05-21T07:52:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:52:53+00:00</t>
+    <t>2025-05-21T08:04:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -38,7 +38,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Mapping du modèle métier PersonneStructure/CDA/FHIR</t>
+    <t>Mapping Métier/CDA/FHIR : "Personne / Structure (RelatedEntity)"</t>
   </si>
   <si>
     <t>Title</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T08:04:56+00:00</t>
+    <t>2025-05-21T13:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -83,10 +83,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Ce ConceptMap présente deux groupes de mapping : 
- - Groupe Mapping 1 : entre le modèle métier de la personne et/ou structure et l'élément CDA relatedEntity
- - Groupe Mapping 2 : entre l'élément CDA relatedEntity et le profil FHIR FrRelatedPersonDocument
- - Groupe Mapping 3 : entre l'élément CDA relatedEntity et l'élément FHIR Patient.contact</t>
+    <t xml:space="preserve">Ce ConceptMap présente trois groupes de mapping: 
+ - Mapping 1 : entre le modèle métier \"PersonneStructure\" et l'élément CDA \"relatedEntity\"
+ - Mapping 2 : entre l'élément CDA \"relatedEntity\" et le profil FHIR \"FrRelatedPersonDocument\"
+ - Mapping 3 : entre l'élément CDA \"relatedEntity\" et l'élément FHIR \"Patient.contact\" </t>
   </si>
   <si>
     <t>Purpose</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T13:48:36+00:00</t>
+    <t>2025-05-23T10:50:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -83,7 +83,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce ConceptMap présente trois groupes de mapping: 
+    <t xml:space="preserve">Ce ConceptMap de l'élément PersonneStructure présente trois groupes de mapping: 
  - Mapping 1 : entre le modèle métier \"PersonneStructure\" et l'élément CDA \"relatedEntity\"
  - Mapping 2 : entre l'élément CDA \"relatedEntity\" et le profil FHIR \"FrRelatedPersonDocument\"
  - Mapping 3 : entre l'élément CDA \"relatedEntity\" et l'élément FHIR \"Patient.contact\" </t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T10:50:09+00:00</t>
+    <t>2025-05-23T12:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
